--- a/data/trans_orig/P1001-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1001-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2007</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95512</t>
+          <t>93297</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>135153</t>
+          <t>135136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>156250</t>
+          <t>156122</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>204794</t>
+          <t>205331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>263600</t>
+          <t>263420</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>324681</t>
+          <t>329422</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>896570</t>
+          <t>896587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>936211</t>
+          <t>938426</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1110319</t>
+          <t>1109782</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1158863</t>
+          <t>1158991</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2022154</t>
+          <t>2017413</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2083235</t>
+          <t>2083415</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,78%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46752</t>
+          <t>46735</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79070</t>
+          <t>77423</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92940</t>
+          <t>92555</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133930</t>
+          <t>133535</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144809</t>
+          <t>148873</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>198758</t>
+          <t>199448</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1614343</t>
+          <t>1615990</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1646661</t>
+          <t>1646678</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1453743</t>
+          <t>1454138</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1494733</t>
+          <t>1495118</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3082328</t>
+          <t>3081638</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3136277</t>
+          <t>3132213</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14060</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33138</t>
+          <t>34163</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18688</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38856</t>
+          <t>38736</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36178</t>
+          <t>37054</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64637</t>
+          <t>63802</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518270</t>
+          <t>517245</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>537348</t>
+          <t>537448</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>437556</t>
+          <t>437676</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457724</t>
+          <t>458966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>963183</t>
+          <t>964018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>991642</t>
+          <t>990766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172453</t>
+          <t>171962</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>225005</t>
+          <t>228714</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>283244</t>
+          <t>285475</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>354868</t>
+          <t>353205</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1812,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>10,45%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>516514</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>475327</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>557935</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>8,38%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>516514</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>472859</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>560462</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3051538</t>
+          <t>3047829</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3104090</t>
+          <t>3104581</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3024329</t>
+          <t>3025992</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3095953</t>
+          <t>3093722</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1925,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>91,55%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>6007</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>6139227</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>6097806</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6180414</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>92,24%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>91,62%</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>6007</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>6139227</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>6095279</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6182882</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>92,24%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2012</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106074</t>
+          <t>109113</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>151873</t>
+          <t>152713</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>291723</t>
+          <t>289585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>357134</t>
+          <t>357688</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>411899</t>
+          <t>413747</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>489247</t>
+          <t>488767</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>822770</t>
+          <t>821930</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>868569</t>
+          <t>865530</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>979608</t>
+          <t>979054</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1045019</t>
+          <t>1047157</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1822138</t>
+          <t>1822618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1899486</t>
+          <t>1897638</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,1%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73778</t>
+          <t>72213</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112123</t>
+          <t>113564</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>147992</t>
+          <t>147808</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>200492</t>
+          <t>202334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>236548</t>
+          <t>232188</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>307990</t>
+          <t>297034</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1849844</t>
+          <t>1848403</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1888189</t>
+          <t>1889754</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1557311</t>
+          <t>1555469</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1609811</t>
+          <t>1609995</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3411779</t>
+          <t>3422735</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3483221</t>
+          <t>3487581</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,76%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13355</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36872</t>
+          <t>38650</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>15787</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35044</t>
+          <t>35816</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33427</t>
+          <t>33695</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65374</t>
+          <t>64003</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>444309</t>
+          <t>442531</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>467826</t>
+          <t>467678</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>423587</t>
+          <t>422815</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>443756</t>
+          <t>442844</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>874439</t>
+          <t>875810</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>906386</t>
+          <t>906118</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211850</t>
+          <t>213584</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>278792</t>
+          <t>273735</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>478911</t>
+          <t>481085</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>565466</t>
+          <t>567568</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>704252</t>
+          <t>707927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>812700</t>
+          <t>818191</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3138999</t>
+          <t>3144056</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3205941</t>
+          <t>3204207</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2987709</t>
+          <t>2985607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3074264</t>
+          <t>3072090</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6158266</t>
+          <t>6152775</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6266714</t>
+          <t>6263039</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2016</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55068</t>
+          <t>53846</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87249</t>
+          <t>87130</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>197551</t>
+          <t>200192</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>253529</t>
+          <t>255834</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>263879</t>
+          <t>265000</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>332481</t>
+          <t>326018</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>667098</t>
+          <t>667217</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>699279</t>
+          <t>700501</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>741131</t>
+          <t>738826</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>797109</t>
+          <t>794468</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1416526</t>
+          <t>1422989</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1485128</t>
+          <t>1484007</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,85%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>99520</t>
+          <t>98913</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>142010</t>
+          <t>143584</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>148309</t>
+          <t>147243</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>197868</t>
+          <t>199260</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>260622</t>
+          <t>258653</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>329173</t>
+          <t>325256</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1934375</t>
+          <t>1932801</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1976865</t>
+          <t>1977472</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1790432</t>
+          <t>1789040</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1839991</t>
+          <t>1841057</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3735512</t>
+          <t>3739429</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3804063</t>
+          <t>3806032</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9297</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25674</t>
+          <t>26728</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23448</t>
+          <t>23905</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46920</t>
+          <t>46220</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36472</t>
+          <t>37893</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65641</t>
+          <t>66777</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>521212</t>
+          <t>520158</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>537596</t>
+          <t>537589</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>502220</t>
+          <t>502920</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>525692</t>
+          <t>525235</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1030386</t>
+          <t>1029250</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1059555</t>
+          <t>1058134</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>177812</t>
+          <t>182458</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>234416</t>
+          <t>238346</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>390957</t>
+          <t>395525</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>472695</t>
+          <t>476170</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>590009</t>
+          <t>589825</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>692303</t>
+          <t>690164</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3143202</t>
+          <t>3139272</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3199806</t>
+          <t>3195160</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3059405</t>
+          <t>3055930</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3141143</t>
+          <t>3136575</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6217415</t>
+          <t>6219554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6319709</t>
+          <t>6319893</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2023</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48174</t>
+          <t>48879</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74863</t>
+          <t>74567</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>157943</t>
+          <t>156915</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>193006</t>
+          <t>195857</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214577</t>
+          <t>212004</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>260210</t>
+          <t>259040</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>439440</t>
+          <t>439736</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>466129</t>
+          <t>465424</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>561110</t>
+          <t>558259</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>596173</t>
+          <t>597201</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1008209</t>
+          <t>1009379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1053842</t>
+          <t>1056415</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,29%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74896</t>
+          <t>74464</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138949</t>
+          <t>141154</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122674</t>
+          <t>130720</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>204257</t>
+          <t>205083</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>226628</t>
+          <t>229267</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>325234</t>
+          <t>329258</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2150808</t>
+          <t>2148603</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2214861</t>
+          <t>2215293</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2032600</t>
+          <t>2031774</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2114183</t>
+          <t>2106137</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4201380</t>
+          <t>4197356</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4299986</t>
+          <t>4297347</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17609</t>
+          <t>17565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38880</t>
+          <t>38679</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37807</t>
+          <t>36812</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62915</t>
+          <t>61212</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59555</t>
+          <t>58932</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94018</t>
+          <t>93178</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>607743</t>
+          <t>607944</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>629014</t>
+          <t>629058</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>597548</t>
+          <t>599251</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>622656</t>
+          <t>623651</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1213068</t>
+          <t>1213908</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1247531</t>
+          <t>1248154</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>153165</t>
+          <t>151143</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>233381</t>
+          <t>231047</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>323227</t>
+          <t>324541</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>440262</t>
+          <t>439659</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>509052</t>
+          <t>515094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>644092</t>
+          <t>652771</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3217302</t>
+          <t>3219636</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3297518</t>
+          <t>3299540</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3211174</t>
+          <t>3211777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3328209</t>
+          <t>3326895</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6458026</t>
+          <t>6449347</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6593066</t>
+          <t>6587024</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1001-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1001-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93297</t>
+          <t>96501</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>135136</t>
+          <t>138261</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>156122</t>
+          <t>153615</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>205331</t>
+          <t>206065</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>263420</t>
+          <t>263011</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>329422</t>
+          <t>325284</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>896587</t>
+          <t>893462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>938426</t>
+          <t>935222</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1109782</t>
+          <t>1109048</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1158991</t>
+          <t>1161498</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2017413</t>
+          <t>2021551</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2083415</t>
+          <t>2083824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,79%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46735</t>
+          <t>47097</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77423</t>
+          <t>77595</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92555</t>
+          <t>92855</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133535</t>
+          <t>132480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>148873</t>
+          <t>148264</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>199448</t>
+          <t>201695</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1615990</t>
+          <t>1615818</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1646678</t>
+          <t>1646316</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1454138</t>
+          <t>1455193</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1495118</t>
+          <t>1494818</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3081638</t>
+          <t>3079391</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3132213</t>
+          <t>3132822</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13960</t>
+          <t>14161</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34163</t>
+          <t>33328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17446</t>
+          <t>18244</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38736</t>
+          <t>37983</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37054</t>
+          <t>37250</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63802</t>
+          <t>67248</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517245</t>
+          <t>518080</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>537448</t>
+          <t>537247</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>437676</t>
+          <t>438429</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>458966</t>
+          <t>458168</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>964018</t>
+          <t>960572</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>990766</t>
+          <t>990570</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171962</t>
+          <t>171921</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>228714</t>
+          <t>227118</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>285475</t>
+          <t>284255</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>353205</t>
+          <t>353412</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>475327</t>
+          <t>473518</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>557935</t>
+          <t>564186</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3047829</t>
+          <t>3049425</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3104581</t>
+          <t>3104622</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3025992</t>
+          <t>3025785</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3093722</t>
+          <t>3094942</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6097806</t>
+          <t>6091555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6180414</t>
+          <t>6182223</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109113</t>
+          <t>108970</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>152713</t>
+          <t>153646</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>289585</t>
+          <t>292423</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>357688</t>
+          <t>356225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>413747</t>
+          <t>413365</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>488767</t>
+          <t>491920</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>821930</t>
+          <t>820997</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>865530</t>
+          <t>865673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>979054</t>
+          <t>980517</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1047157</t>
+          <t>1044319</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1822618</t>
+          <t>1819465</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1897638</t>
+          <t>1898020</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,12%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72213</t>
+          <t>72331</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113564</t>
+          <t>111937</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>147808</t>
+          <t>148849</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>202334</t>
+          <t>200720</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>232188</t>
+          <t>232241</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>297034</t>
+          <t>298278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1848403</t>
+          <t>1850030</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1889754</t>
+          <t>1889636</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1555469</t>
+          <t>1557083</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1609995</t>
+          <t>1608954</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3422735</t>
+          <t>3421491</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3487581</t>
+          <t>3487528</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13062</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38650</t>
+          <t>35837</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15787</t>
+          <t>15119</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35816</t>
+          <t>35810</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,47 +3072,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>46128</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>62229</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>3,44%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>46128</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>33695</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>64003</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>442531</t>
+          <t>445344</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>467678</t>
+          <t>468119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>422815</t>
+          <t>422821</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>442844</t>
+          <t>443512</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3190,42 +3190,42 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>96,7%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>893685</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>877584</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>907439</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>93,38%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>96,56%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>893685</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>875810</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>906118</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>95,09%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>93,19%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>213584</t>
+          <t>211548</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>273735</t>
+          <t>271732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>481085</t>
+          <t>477990</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>567568</t>
+          <t>567428</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>707927</t>
+          <t>704765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>818191</t>
+          <t>814975</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3144056</t>
+          <t>3146059</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3204207</t>
+          <t>3206243</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2985607</t>
+          <t>2985747</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3072090</t>
+          <t>3075185</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6152775</t>
+          <t>6155991</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6263039</t>
+          <t>6266201</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53846</t>
+          <t>55099</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87130</t>
+          <t>86357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>200192</t>
+          <t>199479</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>255834</t>
+          <t>255700</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>265000</t>
+          <t>262286</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>326018</t>
+          <t>329901</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>667217</t>
+          <t>667990</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>700501</t>
+          <t>699248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>738826</t>
+          <t>738960</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>794468</t>
+          <t>795181</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1422989</t>
+          <t>1419106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1484007</t>
+          <t>1486721</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,0%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98913</t>
+          <t>98820</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143584</t>
+          <t>143493</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>147243</t>
+          <t>145920</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>199260</t>
+          <t>197129</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>258653</t>
+          <t>259542</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>325256</t>
+          <t>329476</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1932801</t>
+          <t>1932892</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1977472</t>
+          <t>1977565</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1789040</t>
+          <t>1791171</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1841057</t>
+          <t>1842380</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3739429</t>
+          <t>3735209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3806032</t>
+          <t>3805143</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9297</t>
+          <t>9491</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26728</t>
+          <t>26828</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23905</t>
+          <t>22631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46220</t>
+          <t>45765</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37893</t>
+          <t>36728</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66777</t>
+          <t>64534</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520158</t>
+          <t>520058</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>537589</t>
+          <t>537395</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>502920</t>
+          <t>503375</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>525235</t>
+          <t>526509</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1029250</t>
+          <t>1031493</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1058134</t>
+          <t>1059299</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>182458</t>
+          <t>179380</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>238346</t>
+          <t>237131</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>395525</t>
+          <t>394144</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>476170</t>
+          <t>476102</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>589825</t>
+          <t>591038</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>690164</t>
+          <t>685223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3139272</t>
+          <t>3140487</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3195160</t>
+          <t>3198238</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3055930</t>
+          <t>3055998</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3136575</t>
+          <t>3137956</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6219554</t>
+          <t>6224495</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6319893</t>
+          <t>6318680</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>60187</t>
+          <t>64598</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48879</t>
+          <t>51764</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74567</t>
+          <t>78654</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>175007</t>
+          <t>187015</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>156915</t>
+          <t>168842</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>195857</t>
+          <t>207162</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>235194</t>
+          <t>251613</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>212004</t>
+          <t>229826</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>259040</t>
+          <t>277958</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>454116</t>
+          <t>513316</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>439736</t>
+          <t>499260</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>465424</t>
+          <t>526150</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>579109</t>
+          <t>633586</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>558259</t>
+          <t>613439</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>597201</t>
+          <t>651759</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1033225</t>
+          <t>1146902</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1009379</t>
+          <t>1120557</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1056415</t>
+          <t>1168689</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,57%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514303</t>
+          <t>577914</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514303</t>
+          <t>577914</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514303</t>
+          <t>577914</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>754116</t>
+          <t>820601</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>754116</t>
+          <t>820601</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>754116</t>
+          <t>820601</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1268419</t>
+          <t>1398515</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1268419</t>
+          <t>1398515</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1268419</t>
+          <t>1398515</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>111510</t>
+          <t>118828</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74464</t>
+          <t>98567</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>141154</t>
+          <t>147761</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>170216</t>
+          <t>193182</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130720</t>
+          <t>169556</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>205083</t>
+          <t>217419</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>281726</t>
+          <t>312010</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>229267</t>
+          <t>281289</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>329258</t>
+          <t>352463</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2178247</t>
+          <t>2111152</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2148603</t>
+          <t>2082219</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2215293</t>
+          <t>2131413</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2066641</t>
+          <t>1977201</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2031774</t>
+          <t>1952964</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2106137</t>
+          <t>2000827</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4244888</t>
+          <t>4088353</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4197356</t>
+          <t>4047900</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4297347</t>
+          <t>4119074</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289757</t>
+          <t>2229980</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289757</t>
+          <t>2229980</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289757</t>
+          <t>2229980</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2236857</t>
+          <t>2170383</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236857</t>
+          <t>2170383</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2236857</t>
+          <t>2170383</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4526614</t>
+          <t>4400363</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4526614</t>
+          <t>4400363</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4526614</t>
+          <t>4400363</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26591</t>
+          <t>28815</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17565</t>
+          <t>18557</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38679</t>
+          <t>41289</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>48552</t>
+          <t>56420</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36812</t>
+          <t>44430</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61212</t>
+          <t>71706</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>75143</t>
+          <t>85235</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58932</t>
+          <t>68908</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93178</t>
+          <t>103939</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>620032</t>
+          <t>682772</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>607944</t>
+          <t>670298</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>629058</t>
+          <t>693030</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>611911</t>
+          <t>678457</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>599251</t>
+          <t>663171</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>623651</t>
+          <t>690447</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1231943</t>
+          <t>1361229</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1213908</t>
+          <t>1342525</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1248154</t>
+          <t>1377556</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>198288</t>
+          <t>212241</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>151143</t>
+          <t>186468</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>231047</t>
+          <t>245083</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>393775</t>
+          <t>436617</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>324541</t>
+          <t>405941</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>439659</t>
+          <t>471653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>592063</t>
+          <t>648858</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>515094</t>
+          <t>603563</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>652771</t>
+          <t>693962</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3252395</t>
+          <t>3307240</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3219636</t>
+          <t>3274398</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3299540</t>
+          <t>3333013</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3257661</t>
+          <t>3289244</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3211777</t>
+          <t>3254208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3326895</t>
+          <t>3319920</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6510055</t>
+          <t>6596485</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6449347</t>
+          <t>6551381</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6587024</t>
+          <t>6641780</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>91,67%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450683</t>
+          <t>3519481</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450683</t>
+          <t>3519481</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450683</t>
+          <t>3519481</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3651436</t>
+          <t>3725861</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3651436</t>
+          <t>3725861</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3651436</t>
+          <t>3725861</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7102118</t>
+          <t>7245343</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7102118</t>
+          <t>7245343</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7102118</t>
+          <t>7245343</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
